--- a/data/trans_bre/IP28_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,77</t>
+          <t>-1,91; 1,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,85</t>
+          <t>-3,12; 3,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,71</t>
+          <t>-2,23; 1,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,57</t>
+          <t>-1,02; 4,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 380,14</t>
+          <t>-100,0; 472,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,23</t>
+          <t>-1,92; 2,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,15</t>
+          <t>-3,46; 0,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,64</t>
+          <t>-1,62; 1,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,27</t>
+          <t>-2,54; -0,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,29; 367,8</t>
+          <t>-81,74; 410,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,66</t>
+          <t>-3,45; 0,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,79</t>
+          <t>-1,07; 2,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,09</t>
+          <t>-2,55; 1,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,91</t>
+          <t>-1,36; 3,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 512,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,23</t>
+          <t>-0,61; 3,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,22</t>
+          <t>-0,35; 4,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,77</t>
+          <t>-0,68; 3,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,79</t>
+          <t>-0,79; 3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 713,38</t>
+          <t>-30,48; 624,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,11</t>
+          <t>-0,83; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,66</t>
+          <t>-0,87; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,27 +1075,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,63</t>
+          <t>-0,44; 1,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 160,18</t>
+          <t>-52,87; 153,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 152,11</t>
+          <t>-39,04; 140,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 155,35</t>
+          <t>-65,23; 153,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 272,34</t>
+          <t>-36,87; 277,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,78</t>
+          <t>-1,96; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,12</t>
+          <t>-2,92; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,16</t>
+          <t>-2,29; 1,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,77</t>
+          <t>-1,2; 4,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 472,0</t>
+          <t>-89,37; 521,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,11</t>
+          <t>-2,11; 2,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,01</t>
+          <t>-3,36; 0,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,58</t>
+          <t>-1,64; 1,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,28</t>
+          <t>-2,64; -0,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,74; 410,82</t>
+          <t>-86,43; 341,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 107,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,75</t>
+          <t>-3,52; 0,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,95</t>
+          <t>-0,82; 2,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,03</t>
+          <t>-2,98; 1,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,95</t>
+          <t>-1,28; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,05</t>
+          <t>-0,59; 3,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,67</t>
+          <t>-0,19; 5,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,1</t>
+          <t>-0,68; 2,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,69</t>
+          <t>-0,66; 3,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 624,38</t>
+          <t>-29,64; 701,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,12</t>
+          <t>-0,91; 1,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,59</t>
+          <t>-0,84; 1,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,84</t>
+          <t>-0,86; 0,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,63</t>
+          <t>-0,49; 1,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-52,87; 153,6</t>
+          <t>-51,47; 155,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 140,6</t>
+          <t>-38,12; 140,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 153,28</t>
+          <t>-62,57; 157,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 277,45</t>
+          <t>-42,76; 295,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>119,79%</t>
+          <t>109,01%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,77</t>
+          <t>-2,0; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,94</t>
+          <t>-3,39; 2,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,19</t>
+          <t>-2,26; 1,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 4,67</t>
+          <t>-1,08; 4,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-89,37; 521,54</t>
+          <t>-100,0; 380,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,08</t>
+          <t>-1,88; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,05</t>
+          <t>-3,47; -0,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,63</t>
+          <t>-1,65; 1,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,27</t>
+          <t>-2,73; -0,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,43; 341,16</t>
+          <t>-80,29; 367,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,09</t>
+          <t>-100,0; 134,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>113,24%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,73</t>
+          <t>-3,58; 0,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,85</t>
+          <t>-1,1; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,06</t>
+          <t>-2,58; 1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,67</t>
+          <t>-0,92; 5,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 512,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>116,57%</t>
+          <t>184,79%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,1</t>
+          <t>-0,52; 3,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,26</t>
+          <t>-0,38; 5,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,76</t>
+          <t>-0,64; 2,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,72</t>
+          <t>-0,31; 4,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 701,51</t>
+          <t>-21,41; 713,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,06</t>
+          <t>-0,92; 1,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,51</t>
+          <t>-0,87; 1,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,85</t>
+          <t>-0,95; 0,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,62</t>
+          <t>-0,41; 1,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-51,47; 155,31</t>
+          <t>-55,44; 160,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 140,67</t>
+          <t>-41,17; 152,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 157,67</t>
+          <t>-64,61; 155,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 295,71</t>
+          <t>-37,23; 326,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP28_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP28_R-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuya percepción de los madres/padres es que su peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,179 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-48,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>109,01%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.03586319612844894</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.05791414008596216</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.5429718321175571</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.088722481140183</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.03789266965474883</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.02642750737293878</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.4885794983677134</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.090109871894116</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,0; 1,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,39; 2,85</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 1,71</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-1,08; 4,71</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 380,14</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.003528476772597</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.387221657460833</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.26462456849451</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.081143187057671</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.769412333799072</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.853260256016608</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.712108436013632</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.712718509128213</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>3.80144077533674</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-80,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 2,23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,47; -0,15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,65; 1,64</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,73; -0,26</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-80,29; 367,8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 134,22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.1046718560755163</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.525943043726834</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.01514591013537011</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.001015525872036</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.06618632005608049</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.8071535082246887</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01530538547247684</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-57,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-39,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>113,24%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.884083956645887</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.468209284231551</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.651764913705391</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.730829322579736</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8028636842341998</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,58; 0,66</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,1; 2,79</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 1,09</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 5,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 512,66</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.232138345872535</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-0.1504948757898991</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.642931494534955</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.2574188409378868</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3.678031690971978</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.342238034005357</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +799,273 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>144,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>127,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>115,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>184,79%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.05512011858432</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5982000891205868</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.5031603048091809</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.548278302755257</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5761917220608465</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.7641296416959936</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3959507647631508</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.132440704788434</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,52; 3,23</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 5,22</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 2,77</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,31; 4,2</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-21,41; 713,38</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.582118709674063</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.10007904061462</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.583125075291554</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.9187757113961439</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6637982796723076</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.786808908509057</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.093676333935809</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.107767634979435</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>5.126624025697207</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9450309306516174</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.175648533774996</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8101021655896727</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.239804151313048</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.445794424658014</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.277023883446415</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.157529762807029</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.847914623960005</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.5239883402217002</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.3819817926077945</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.6364152465966649</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.3083774438045517</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.2141266018227282</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.232244279663096</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.220902664154454</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.766464268961161</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.198794844525155</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>7.13383549762597</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 1,11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 1,66</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; 0,84</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,41; 1,94</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-55,44; 160,18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-41,17; 152,11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-64,61; 155,35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-37,23; 326,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.08599270389807334</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3627752514637639</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.008143490196063467</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6263282298702506</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.06984627803018789</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2189959501464229</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.008158841536641696</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.6209545483134117</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.9180225019575385</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.8682218429876727</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.9535373450124738</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.4067740121605278</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5543537350084948</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4116848768394563</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6460666327854516</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3722730916394555</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.111005234011843</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.660768210013083</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8362450533843127</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.938747403458357</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.60180141758428</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.52113485626649</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.553455108856382</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>3.266120918835711</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1073,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
